--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488275_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488275_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.318</v>
+        <v>4.1865</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7949</v>
+        <v>2.2548</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5231</v>
+        <v>1.9317</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7613</v>
+        <v>4.0921</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1914</v>
+        <v>-1.525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5699</v>
+        <v>5.6171</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1457</v>
+        <v>4.0485</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3992</v>
+        <v>-0.524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7465000000000001</v>
+        <v>4.5725</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6156</v>
+        <v>0.0436</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7922</v>
+        <v>-1.001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1766</v>
+        <v>1.0446</v>
       </c>
       <c r="P2" t="n">
-        <v>1.297</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R2" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2597</v>
+        <v>-0.4244</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6491</v>
+        <v>-0.2552</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3895</v>
+        <v>-0.1691</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.9455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.292</v>
+        <v>3.0795</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6558</v>
+        <v>1.4579</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6362</v>
+        <v>1.6216</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0921</v>
+        <v>1.7613</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.525</v>
+        <v>1.1914</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6171</v>
+        <v>0.5699</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0485</v>
+        <v>1.1457</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.524</v>
+        <v>0.3992</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5725</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0436</v>
+        <v>0.6156</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.001</v>
+        <v>0.7922</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0446</v>
+        <v>-0.1766</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3189</v>
+        <v>0.0211</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.3121</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4646</v>
+        <v>-0.291</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3512</v>
+        <v>2.4491</v>
       </c>
       <c r="E4" t="n">
-        <v>1.604</v>
+        <v>1.7019</v>
       </c>
       <c r="F4" t="n">
         <v>0.7472</v>
@@ -766,10 +766,10 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2014</v>
+        <v>-0.1035</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1269</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0876</v>
+        <v>-0.0395</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1288</v>
+        <v>-0.3065</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2163</v>
+        <v>0.267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3131</v>
+        <v>-1.0518</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06270000000000001</v>
+        <v>-2.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2505</v>
+        <v>1.0118</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7493</v>
+        <v>0.1548</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9152</v>
+        <v>-0.5113</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1659</v>
+        <v>0.666</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0625</v>
+        <v>-1.2065</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9779</v>
+        <v>-1.5522</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.3457</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7411</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>-4.0763</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1117</v>
+        <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>0.767</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>1.159</v>
+        <v>-0.4759</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.392</v>
+        <v>-0.3694</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2514</v>
+        <v>3.5251</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>4.091</v>
       </c>
       <c r="X6" t="n">
         <v>-0.5659</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5533</v>
+        <v>-0.6111</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0383</v>
+        <v>-1.8028</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.515</v>
+        <v>1.1917</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0417</v>
+        <v>0.3131</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4329</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4747</v>
+        <v>0.2505</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.527</v>
+        <v>-0.7493</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6099</v>
+        <v>-0.9152</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>0.1659</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5687</v>
+        <v>1.0625</v>
       </c>
       <c r="N7" t="n">
-        <v>0.177</v>
+        <v>0.9779</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3917</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3706</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2932</v>
+        <v>0.0684</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4887</v>
+        <v>0.485</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1955</v>
+        <v>-0.4166</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2589</v>
+        <v>-0.2514</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>-0.5659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7486</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7097</v>
+        <v>-0.332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0208</v>
+        <v>-0.4166</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0518</v>
+        <v>0.0417</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0635</v>
+        <v>-0.4329</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0118</v>
+        <v>0.4747</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1548</v>
+        <v>-0.527</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5113</v>
+        <v>-0.6099</v>
       </c>
       <c r="L8" t="n">
-        <v>0.666</v>
+        <v>0.0829</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2065</v>
+        <v>0.5687</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5522</v>
+        <v>0.177</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3457</v>
+        <v>0.3917</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0763</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4087</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4947</v>
+        <v>0.0979</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8792</v>
+        <v>0.1949</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6156</v>
+        <v>-0.097</v>
       </c>
       <c r="V8" t="n">
-        <v>3.5251</v>
+        <v>-1.2589</v>
       </c>
       <c r="W8" t="n">
-        <v>4.091</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5659</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.321</v>
+        <v>-1.9841</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1141</v>
+        <v>-0.1797</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4352</v>
+        <v>-1.8045</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9184</v>
@@ -1156,13 +1156,13 @@
         <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4862</v>
+        <v>-0.1769</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1679</v>
+        <v>-0.4616</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6541</v>
+        <v>0.2848</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2594</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1872</v>
+        <v>-4.33</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7944</v>
+        <v>-4.6418</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6072</v>
+        <v>0.3118</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2836</v>
@@ -1234,13 +1234,13 @@
         <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6521</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6392</v>
+        <v>-0.4865</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.013</v>
+        <v>-0.3084</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2514</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.889</v>
+        <v>-7.0453</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.7808</v>
+        <v>-6.8879</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1082</v>
+        <v>-0.1574</v>
       </c>
       <c r="G11" t="n">
         <v>-6.4456</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3386</v>
+        <v>-0.4949</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4014</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0629</v>
+        <v>0.0136</v>
       </c>
       <c r="V11" t="n">
         <v>1.0069</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.268600000000001</v>
+        <v>-4.7214</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.9611</v>
+        <v>-8.414000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>3.692399999999999</v>
+        <v>3.6925</v>
       </c>
       <c r="G12" t="n">
         <v>-5.737899999999999</v>
@@ -1390,16 +1390,16 @@
         <v>13.8965</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.3265</v>
+        <v>-2.7794</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8466</v>
+        <v>-1.2993</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4801</v>
+        <v>-1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>4.7222</v>
+        <v>4.722200000000001</v>
       </c>
       <c r="W12" t="n">
         <v>10.0686</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8154</v>
+        <v>4.5153</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1854</v>
+        <v>2.471</v>
       </c>
       <c r="F13" t="n">
-        <v>5.0008</v>
+        <v>2.0443</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5113</v>
+        <v>2.0881</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1976</v>
+        <v>1.8668</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3137</v>
+        <v>0.2213</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7785</v>
+        <v>1.3553</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6956</v>
+        <v>1.3648</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0829</v>
+        <v>-0.0094</v>
       </c>
       <c r="M13" t="n">
         <v>0.7328</v>
@@ -1459,37 +1459,37 @@
         <v>0.2307</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7411</v>
+        <v>2.0382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
         <v>2.9646</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7865</v>
+        <v>0.3895</v>
       </c>
       <c r="T13" t="n">
-        <v>1.113</v>
+        <v>-0.1601</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6735</v>
+        <v>0.5496</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2589</v>
+        <v>-0.0005</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6289</v>
+        <v>2.2022</v>
       </c>
       <c r="X13" t="n">
-        <v>0.63</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3791</v>
+        <v>4.2113</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7855</v>
+        <v>-0.8709</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5936</v>
+        <v>5.0821</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0881</v>
+        <v>2.5113</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8668</v>
+        <v>2.1976</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2213</v>
+        <v>0.3137</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3553</v>
+        <v>1.7785</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3648</v>
+        <v>1.6956</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0094</v>
+        <v>0.0829</v>
       </c>
       <c r="M14" t="n">
         <v>0.7328</v>
@@ -1537,31 +1537,31 @@
         <v>0.2307</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0382</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R14" t="n">
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7466</v>
+        <v>1.1823</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8456</v>
+        <v>0.4275</v>
       </c>
       <c r="U14" t="n">
-        <v>0.099</v>
+        <v>0.7548</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.0005</v>
+        <v>1.2589</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2022</v>
+        <v>0.6289</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2027</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8785</v>
+        <v>1.6821</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4725</v>
+        <v>1.3745</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4061</v>
+        <v>0.3076</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1441</v>
@@ -1624,13 +1624,13 @@
         <v>0.1853</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5785</v>
+        <v>0.3821</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4887</v>
+        <v>0.3908</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0898</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.2589</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9394</v>
+        <v>1.0877</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8461</v>
+        <v>0.7482</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.3395</v>
       </c>
       <c r="G16" t="n">
         <v>1.1371</v>
@@ -1702,13 +1702,13 @@
         <v>0.7411</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0124</v>
+        <v>0.1359</v>
       </c>
       <c r="T16" t="n">
-        <v>0.291</v>
+        <v>0.1931</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3034</v>
+        <v>-0.0572</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6292</v>
+        <v>0.6107</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6172</v>
+        <v>-1.5243</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.988</v>
+        <v>2.135</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9961</v>
+        <v>0.1157</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4368</v>
+        <v>1.2523</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5592</v>
+        <v>-1.1366</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5713</v>
+        <v>-1.2373</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8971</v>
+        <v>0.0684</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6742</v>
+        <v>-1.3057</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4247</v>
+        <v>1.353</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5397</v>
+        <v>1.1839</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.115</v>
+        <v>0.1692</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6685</v>
+        <v>0.7156</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6579</v>
+        <v>0.028</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0107</v>
+        <v>0.6877</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.1471</v>
+        <v>-1.8883</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.4616</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1388</v>
+        <v>0.2461</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1118</v>
+        <v>1.0296</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2506</v>
+        <v>-0.7836</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1157</v>
+        <v>1.9961</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2523</v>
+        <v>1.4368</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1366</v>
+        <v>0.5592</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2373</v>
+        <v>1.5713</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0684</v>
+        <v>0.8971</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3057</v>
+        <v>0.6742</v>
       </c>
       <c r="M19" t="n">
-        <v>1.353</v>
+        <v>0.4247</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1839</v>
+        <v>0.5397</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1692</v>
+        <v>-0.115</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2437</v>
+        <v>0.2854</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5596</v>
+        <v>0.0703</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8033</v>
+        <v>0.2151</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8883</v>
+        <v>-3.1471</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5733</v>
+        <v>-3.4616</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0547</v>
       </c>
       <c r="F20" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="G20" t="n">
         <v>0.2611</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1689</v>
+        <v>-0.1443</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8596</v>
+        <v>-0.6895</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3105</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5491</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0737</v>
@@ -2092,13 +2092,13 @@
         <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1564</v>
+        <v>0.0137</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4501</v>
+        <v>-0.0584</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2937</v>
+        <v>0.0721</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.931</v>
+        <v>-1.5976</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9397</v>
+        <v>-0.7538</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0087</v>
+        <v>-0.8438</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5033</v>
+        <v>-0.2178</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5399</v>
+        <v>0.4811</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0366</v>
+        <v>-0.6989</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1246</v>
+        <v>0.0429</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0002</v>
+        <v>0.0429</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8756</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3788</v>
+        <v>-0.2607</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5397</v>
+        <v>0.4381</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.161</v>
+        <v>-0.6989</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.308</v>
+        <v>-0.139</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5696</v>
+        <v>0.1296</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7383999999999999</v>
+        <v>-0.2686</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8894</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0016</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8877</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9653</v>
+        <v>-2.2436</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0476</v>
+        <v>-2.1839</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9176</v>
+        <v>-0.0597</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2178</v>
+        <v>-1.7614</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4811</v>
+        <v>-0.5403</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6989</v>
+        <v>-1.2211</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0429</v>
+        <v>-1.5936</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0429</v>
+        <v>-0.9407</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.6529</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2607</v>
+        <v>-0.1678</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4381</v>
+        <v>0.4004</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6989</v>
+        <v>-0.5683</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9264</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5066000000000001</v>
+        <v>0.259</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1641</v>
+        <v>0.3361</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3425</v>
+        <v>-0.0771</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1703</v>
+        <v>-2.3399</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.086</v>
+        <v>-4.3314</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0843</v>
+        <v>1.9916</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7614</v>
+        <v>0.5033</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5403</v>
+        <v>2.5399</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2211</v>
+        <v>-2.0366</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5936</v>
+        <v>0.1246</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9407</v>
+        <v>2.0002</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6529</v>
+        <v>-1.8756</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1678</v>
+        <v>0.3788</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4004</v>
+        <v>0.5397</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5683</v>
+        <v>-0.161</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7411</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9264</v>
+        <v>-4.6322</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1853</v>
+        <v>2.7793</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3323</v>
+        <v>0.8991</v>
       </c>
       <c r="T24" t="n">
-        <v>0.434</v>
+        <v>0.1779</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1017</v>
+        <v>0.7212</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.8894</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.268599999999999</v>
+        <v>5.921599999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6923</v>
+        <v>-3.6924</v>
       </c>
       <c r="F25" t="n">
-        <v>8.961099999999998</v>
+        <v>9.613899999999997</v>
       </c>
       <c r="G25" t="n">
-        <v>5.7378</v>
+        <v>5.737799999999999</v>
       </c>
       <c r="H25" t="n">
         <v>11.7655</v>
@@ -2386,16 +2386,16 @@
         <v>-3.6872</v>
       </c>
       <c r="M25" t="n">
-        <v>2.3603</v>
+        <v>2.360300000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7007</v>
+        <v>4.700699999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-2.3408</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9265999999999991</v>
+        <v>0.9265999999999992</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.8963</v>
@@ -2404,13 +2404,13 @@
         <v>14.823</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3266</v>
+        <v>3.9793</v>
       </c>
       <c r="T25" t="n">
         <v>1.4801</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8466</v>
+        <v>2.4994</v>
       </c>
       <c r="V25" t="n">
         <v>-4.721900000000001</v>
